--- a/resultados/siqueiracampos/erros_varredura.xlsx
+++ b/resultados/siqueiracampos/erros_varredura.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/resultados/siqueiracampos/erros_varredura.xlsx
+++ b/resultados/siqueiracampos/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F249"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7392,6 +7392,258 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2505/feira-de-adocao-concurso-de-pet-caopanha-do-agasalho/wa.me/5543984376305</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D250" t="n">
+        <v>404</v>
+      </c>
+      <c r="E250" t="n">
+        <v>5</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>2026-08-05 15:29:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>http://www.doe.siqueiracampos.pr.gov.br/?fbclid=IwAR3eDHjJouW3L7_0NcQzg_Qx6F0VOK5aILzZUnyNPdF7IhISkl1w1suJmwU</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TIMEOUT_OU_CONEXAO</t>
+        </is>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:38:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>http://www.doe.siqueiracampos.pr.gov.br/?fbclid=IwAR3eDHjJouW3L7_0NcQzg_Qx6F0VOK5aILzZUnyNPdF7IhISkl1w1suJmwU</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: WebDriverException</t>
+        </is>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>5</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:38:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/pagina/10/eu-faco</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D253" t="n">
+        <v>500</v>
+      </c>
+      <c r="E253" t="n">
+        <v>5</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:40:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2610/festival-de-inverno-2023-2-edicao-sabores-musica-e-diversao-em-siqueira-campos/wa.me/554384376305</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>404</v>
+      </c>
+      <c r="E254" t="n">
+        <v>5</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:41:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2601/1-festival-de-compositores-de-siqueira-campos-abre-inscricoes-para-compositores-da-regiao/wa.me/5543984376305</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D255" t="n">
+        <v>404</v>
+      </c>
+      <c r="E255" t="n">
+        <v>5</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/2601/1-festival-de-compositores-de-siqueira-campos-abre-inscricoes-para-compositores-da-regiao/wa.me/5511964288173</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D256" t="n">
+        <v>404</v>
+      </c>
+      <c r="E256" t="n">
+        <v>5</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:41:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/print-noticia/2384/ratinho-junior-anuncia-mais-de-r84-milhoes-para-siqueira-campos-e-regiao/Modernização no aeroporto de Siqueira Campos impactará todo o Norte Pioneiro</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D257" t="n">
+        <v>404</v>
+      </c>
+      <c r="E257" t="n">
+        <v>5</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>2026-08-05 16:53:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>siqueiracampos</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://www.siqueiracampos.pr.gov.br/noticia/print-noticia/2505/feira-de-adocao-concurso-de-pet-caopanha-do-agasalho/wa.me/5543984376305</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D258" t="n">
+        <v>404</v>
+      </c>
+      <c r="E258" t="n">
+        <v>6</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>2026-08-05 17:57:19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
